--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.66836493890398</v>
+        <v>7.746109302571898</v>
       </c>
       <c r="D2" t="n">
-        <v>10.36144337337049</v>
+        <v>1.683734548172705</v>
       </c>
       <c r="E2" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F2" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.43302602024789</v>
+        <v>5.757866728290283</v>
       </c>
       <c r="D3" t="n">
-        <v>34.12218244362517</v>
+        <v>5.544854647089091</v>
       </c>
       <c r="E3" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F3" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.58108272764591</v>
+        <v>5.78192594324246</v>
       </c>
       <c r="D4" t="n">
-        <v>33.69511348042035</v>
+        <v>5.475455940568308</v>
       </c>
       <c r="E4" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F4" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.24298912908908</v>
+        <v>9.464485733476977</v>
       </c>
       <c r="D5" t="n">
-        <v>54.1116257976997</v>
+        <v>8.793139192126201</v>
       </c>
       <c r="E5" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F5" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.59083007068052</v>
+        <v>5.458509886485585</v>
       </c>
       <c r="D6" t="n">
-        <v>32.95969160672983</v>
+        <v>5.355949886093597</v>
       </c>
       <c r="E6" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F6" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.28480457510676</v>
+        <v>9.633780743454849</v>
       </c>
       <c r="D7" t="n">
-        <v>58.28666799422827</v>
+        <v>9.471583549062094</v>
       </c>
       <c r="E7" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F7" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.156286872124656</v>
+        <v>1.000396616720257</v>
       </c>
       <c r="D8" t="n">
-        <v>4.808913457453317</v>
+        <v>0.7814484368361639</v>
       </c>
       <c r="E8" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F8" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.15972491473551</v>
+        <v>10.75095529864452</v>
       </c>
       <c r="D9" t="n">
-        <v>66.30752969890727</v>
+        <v>10.77497357607243</v>
       </c>
       <c r="E9" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F9" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>75.09923450260939</v>
+        <v>12.20362560667403</v>
       </c>
       <c r="D10" t="n">
-        <v>73.98698118455212</v>
+        <v>12.02288444248972</v>
       </c>
       <c r="E10" t="n">
-        <v>19.84079561281713</v>
+        <v>3.224129287082784</v>
       </c>
       <c r="F10" t="n">
-        <v>22.64010556072768</v>
+        <v>3.679017153618248</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
